--- a/data/trans_camb/P3A_R2-Clase-trans_camb.xlsx
+++ b/data/trans_camb/P3A_R2-Clase-trans_camb.xlsx
@@ -523,7 +523,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares en los que las tareas domésticas las realiza principalmente una persona con remuneración</t>
+          <t>Hogares en los que las tareas domésticas las realiza principalmente una persona con remuneración (por ingresos del hogar o no)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-7,33; 1,22</t>
+          <t>-7,28; 1,05</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-10,23; -1,88</t>
+          <t>-10,56; -2,54</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-8,11; -0,86</t>
+          <t>-8,48; -1,29</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-7,58; 2,04</t>
+          <t>-7,57; 1,59</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-9,27; -0,11</t>
+          <t>-9,01; -0,03</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-7,52; 0,56</t>
+          <t>-7,14; 0,66</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-6,08; 0,25</t>
+          <t>-6,0; 0,19</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-8,4; -2,67</t>
+          <t>-8,31; -2,51</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-6,81; -1,41</t>
+          <t>-6,78; -1,51</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-50,42; 14,9</t>
+          <t>-53,19; 10,97</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-72,55; -16,33</t>
+          <t>-75,06; -24,17</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-56,91; -8,19</t>
+          <t>-58,99; -10,45</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-59,58; 28,14</t>
+          <t>-58,54; 24,67</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-68,44; 2,65</t>
+          <t>-68,76; 2,99</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-55,34; 9,42</t>
+          <t>-53,05; 9,92</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-47,49; 4,23</t>
+          <t>-47,06; 1,87</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-65,28; -25,4</t>
+          <t>-65,93; -26,59</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-51,79; -14,1</t>
+          <t>-51,46; -14,61</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-4,27; 2,61</t>
+          <t>-4,04; 2,45</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-5,78; 0,3</t>
+          <t>-6,12; -0,14</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-4,75; 1,34</t>
+          <t>-4,71; 1,5</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,62; 4,99</t>
+          <t>-1,76; 4,99</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-4,13; 1,28</t>
+          <t>-4,34; 1,25</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-2,16; 2,98</t>
+          <t>-1,99; 2,88</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-2,14; 2,79</t>
+          <t>-2,01; 2,7</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-4,33; -0,24</t>
+          <t>-4,15; -0,26</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-2,31; 1,49</t>
+          <t>-2,39; 1,4</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-58,83; 79,13</t>
+          <t>-58,24; 71,14</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-79,38; 17,62</t>
+          <t>-82,39; 5,45</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-61,79; 39,1</t>
+          <t>-62,79; 43,42</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-37,93; 201,16</t>
+          <t>-36,28; 185,5</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-80,75; 68,57</t>
+          <t>-82,36; 64,74</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-39,0; 118,26</t>
+          <t>-38,92; 122,32</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-37,99; 80,79</t>
+          <t>-37,11; 75,36</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-73,46; -2,18</t>
+          <t>-71,13; 1,89</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-39,51; 46,8</t>
+          <t>-40,78; 44,83</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,91; 1,61</t>
+          <t>-1,93; 1,83</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,86; 0,78</t>
+          <t>-2,6; 1,13</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-2,9; 1,96</t>
+          <t>-3,09; 1,99</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,13; 4,99</t>
+          <t>-1,97; 5,14</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-3,62; 3,64</t>
+          <t>-3,68; 3,01</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,49; 8,29</t>
+          <t>0,71; 8,73</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-1,45; 1,99</t>
+          <t>-1,34; 2,1</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-2,41; 0,77</t>
+          <t>-2,42; 0,73</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-2,11; 2,69</t>
+          <t>-2,15; 2,68</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-59,36; 102,91</t>
+          <t>-54,65; 131,22</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-76,38; 61,94</t>
+          <t>-74,69; 74,81</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-73,07; 101,67</t>
+          <t>-73,77; 104,02</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-56,65; 540,29</t>
+          <t>-65,09; 600,68</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 519,88</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-10,84; 1084,45</t>
+          <t>-7,34; 1098,77</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-40,54; 117,4</t>
+          <t>-38,98; 122,14</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-67,57; 58,91</t>
+          <t>-68,97; 50,08</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-54,94; 135,13</t>
+          <t>-55,09; 130,25</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,71; 1,68</t>
+          <t>-0,63; 1,84</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,22; 0,86</t>
+          <t>-1,24; 0,85</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,31; 4,32</t>
+          <t>1,3; 4,34</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,96; 1,89</t>
+          <t>-0,83; 1,87</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,79; 2,06</t>
+          <t>-0,65; 1,94</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-0,21; 2,81</t>
+          <t>-0,23; 2,73</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-0,45; 1,41</t>
+          <t>-0,46; 1,26</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-0,69; 1,02</t>
+          <t>-0,67; 0,94</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,8; 3,05</t>
+          <t>0,76; 3,14</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-29,78; 121,9</t>
+          <t>-25,86; 128,8</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-49,23; 59,32</t>
+          <t>-49,28; 63,01</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>51,99; 288,34</t>
+          <t>54,89; 304,59</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-57,95; 290,13</t>
+          <t>-54,24; 287,35</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-51,61; 309,76</t>
+          <t>-45,32; 309,08</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-10,67; 438,57</t>
+          <t>-10,02; 401,14</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-23,17; 108,55</t>
+          <t>-23,33; 100,66</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-33,38; 77,8</t>
+          <t>-33,24; 77,79</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>38,4; 220,48</t>
+          <t>38,33; 242,48</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>1,14; 5,39</t>
+          <t>1,22; 5,4</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-0,73; 2,47</t>
+          <t>-0,93; 2,4</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0,63; 4,32</t>
+          <t>0,63; 4,47</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-0,43; 2,93</t>
+          <t>-0,53; 2,79</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-1,99; 0,9</t>
+          <t>-2,01; 0,97</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,43; 4,98</t>
+          <t>1,44; 5,02</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0,75; 3,48</t>
+          <t>0,67; 3,35</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-0,93; 1,24</t>
+          <t>-0,96; 1,14</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1,61; 4,28</t>
+          <t>1,69; 4,44</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>31,49; 1074,43</t>
+          <t>28,53; 1016,61</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-36,92; 450,17</t>
+          <t>-49,2; 446,17</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>10,41; 774,88</t>
+          <t>-8,29; 813,27</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-23,33; 281,69</t>
+          <t>-23,19; 257,21</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-77,84; 106,7</t>
+          <t>-73,46; 123,2</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>46,29; 486,69</t>
+          <t>38,51; 507,63</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>31,5; 368,15</t>
+          <t>26,41; 322,16</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-43,29; 124,93</t>
+          <t>-45,48; 125,16</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>63,69; 450,19</t>
+          <t>76,38; 494,22</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-5,57; 0,89</t>
+          <t>-5,42; 0,55</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-6,25; -0,36</t>
+          <t>-6,16; -0,2</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-4,99; 5,6</t>
+          <t>-5,25; 3,81</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1,88; 5,6</t>
+          <t>2,01; 5,64</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>0,09; 3,45</t>
+          <t>-0,11; 3,49</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>3,04; 6,85</t>
+          <t>3,21; 6,9</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,01; 4,19</t>
+          <t>0,89; 4,04</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-0,71; 2,29</t>
+          <t>-0,76; 2,26</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>1,66; 5,43</t>
+          <t>1,82; 5,23</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-80,83; 46,31</t>
+          <t>-81,46; 25,19</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-90,86; 0,87</t>
+          <t>-88,18; 6,16</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-86,82; 157,66</t>
+          <t>-92,2; 107,79</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>45,73; 230,82</t>
+          <t>51,46; 231,82</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-2,14; 140,66</t>
+          <t>-1,53; 158,11</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>78,64; 289,84</t>
+          <t>81,71; 290,03</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>23,94; 145,84</t>
+          <t>20,93; 150,25</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-18,28; 83,53</t>
+          <t>-19,71; 75,49</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>41,81; 191,22</t>
+          <t>43,21; 194,84</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-1,08; 0,87</t>
+          <t>-1,16; 0,74</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-2,44; -0,7</t>
+          <t>-2,46; -0,76</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-0,96; 1,38</t>
+          <t>-0,92; 1,29</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>0,53; 2,45</t>
+          <t>0,43; 2,37</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-0,92; 0,81</t>
+          <t>-0,96; 0,87</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>1,05; 3,15</t>
+          <t>1,1; 3,12</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-0,13; 1,23</t>
+          <t>-0,03; 1,31</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-1,51; -0,22</t>
+          <t>-1,48; -0,21</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>0,35; 1,91</t>
+          <t>0,38; 1,93</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-24,34; 24,03</t>
+          <t>-25,52; 20,72</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-54,32; -19,79</t>
+          <t>-54,83; -20,44</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-20,98; 37,33</t>
+          <t>-20,1; 35,52</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>14,6; 89,91</t>
+          <t>11,88; 90,85</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-26,79; 29,86</t>
+          <t>-27,34; 31,04</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>29,54; 118,78</t>
+          <t>32,67; 116,6</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-3,33; 36,92</t>
+          <t>-0,61; 40,56</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-37,73; -6,47</t>
+          <t>-37,59; -6,04</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>9,59; 57,09</t>
+          <t>9,6; 59,51</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P3A_R2-Clase-trans_camb.xlsx
+++ b/data/trans_camb/P3A_R2-Clase-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>-4,53</t>
+          <t>-4,64</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-3,02</t>
+          <t>-2,96</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-3,93</t>
+          <t>-3,97</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-7,28; 1,05</t>
+          <t>-7,32; 1,2</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-10,56; -2,54</t>
+          <t>-9,87; -1,94</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-8,48; -1,29</t>
+          <t>-8,07; -0,78</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-7,57; 1,59</t>
+          <t>-7,47; 1,66</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-9,01; -0,03</t>
+          <t>-8,55; 0,26</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-7,14; 0,66</t>
+          <t>-7,28; 1,06</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-6,0; 0,19</t>
+          <t>-6,07; 0,04</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-8,31; -2,51</t>
+          <t>-8,55; -2,61</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-6,78; -1,51</t>
+          <t>-6,65; -1,3</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>-38,55%</t>
+          <t>-39,52%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-29,51%</t>
+          <t>-28,9%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-35,28%</t>
+          <t>-35,56%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-53,19; 10,97</t>
+          <t>-51,66; 12,76</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-75,06; -24,17</t>
+          <t>-72,58; -17,93</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-58,99; -10,45</t>
+          <t>-58,14; -7,72</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-58,54; 24,67</t>
+          <t>-58,36; 21,58</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-68,76; 2,99</t>
+          <t>-68,16; 9,21</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-53,05; 9,92</t>
+          <t>-54,17; 14,41</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-47,06; 1,87</t>
+          <t>-47,57; 0,7</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-65,93; -26,59</t>
+          <t>-66,34; -27,38</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-51,46; -14,61</t>
+          <t>-50,1; -13,45</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-1,27</t>
+          <t>-1,25</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,6</t>
+          <t>1,11</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-0,35</t>
+          <t>-0,1</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-4,04; 2,45</t>
+          <t>-4,09; 2,78</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-6,12; -0,14</t>
+          <t>-5,9; 0,23</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-4,71; 1,5</t>
+          <t>-4,92; 1,39</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,76; 4,99</t>
+          <t>-1,6; 4,98</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-4,34; 1,25</t>
+          <t>-4,16; 1,09</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-1,99; 2,88</t>
+          <t>-1,56; 3,49</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-2,01; 2,7</t>
+          <t>-1,92; 2,72</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-4,15; -0,26</t>
+          <t>-4,27; -0,2</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-2,39; 1,4</t>
+          <t>-2,36; 1,8</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-24,13%</t>
+          <t>-23,83%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>15,73%</t>
+          <t>28,91%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-7,65%</t>
+          <t>-2,21%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-58,24; 71,14</t>
+          <t>-55,59; 77,56</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-82,39; 5,45</t>
+          <t>-80,9; 23,46</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-62,79; 43,42</t>
+          <t>-61,45; 47,64</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-36,28; 185,5</t>
+          <t>-36,85; 193,57</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-82,36; 64,74</t>
+          <t>-79,05; 54,46</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-38,92; 122,32</t>
+          <t>-30,74; 144,49</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-37,11; 75,36</t>
+          <t>-36,11; 81,14</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-71,13; 1,89</t>
+          <t>-72,66; -3,52</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-40,78; 44,83</t>
+          <t>-40,26; 54,72</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>-0,21</t>
+          <t>1,46</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4,61</t>
+          <t>5,03</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0,75</t>
+          <t>2,48</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,93; 1,83</t>
+          <t>-2,06; 1,67</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,6; 1,13</t>
+          <t>-2,69; 0,83</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-3,09; 1,99</t>
+          <t>-0,69; 3,84</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1,97; 5,14</t>
+          <t>-1,78; 5,02</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-3,68; 3,01</t>
+          <t>-3,83; 2,93</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,71; 8,73</t>
+          <t>1,41; 9,13</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-1,34; 2,1</t>
+          <t>-1,35; 1,95</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-2,42; 0,73</t>
+          <t>-2,3; 0,79</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-2,15; 2,68</t>
+          <t>0,67; 4,58</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>-8,12%</t>
+          <t>57,89%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>181,98%</t>
+          <t>198,5%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>29,86%</t>
+          <t>97,94%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-54,65; 131,22</t>
+          <t>-55,76; 109,04</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-74,69; 74,81</t>
+          <t>-75,38; 62,4</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-73,77; 104,02</t>
+          <t>-20,84; 240,08</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-65,09; 600,68</t>
+          <t>-49,79; 633,98</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 519,88</t>
+          <t>-100,0; 442,74</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-7,34; 1098,77</t>
+          <t>10,29; 1157,99</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-38,98; 122,14</t>
+          <t>-42,33; 111,48</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-68,97; 50,08</t>
+          <t>-67,79; 46,43</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-55,09; 130,25</t>
+          <t>14,79; 269,59</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2,75</t>
+          <t>2,7</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,44</t>
+          <t>2,07</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>2,02</t>
+          <t>2,38</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,63; 1,84</t>
+          <t>-0,84; 1,7</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,24; 0,85</t>
+          <t>-1,22; 1,0</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,3; 4,34</t>
+          <t>1,27; 4,33</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,83; 1,87</t>
+          <t>-0,77; 1,7</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,65; 1,94</t>
+          <t>-0,62; 1,97</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-0,23; 2,73</t>
+          <t>0,92; 3,31</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-0,46; 1,26</t>
+          <t>-0,34; 1,37</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-0,67; 0,94</t>
+          <t>-0,73; 0,93</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,76; 3,14</t>
+          <t>1,41; 3,44</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>139,06%</t>
+          <t>136,71%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>119,9%</t>
+          <t>172,05%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>119,32%</t>
+          <t>140,38%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-25,86; 128,8</t>
+          <t>-32,0; 111,64</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-49,28; 63,01</t>
+          <t>-47,41; 71,94</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>54,89; 304,59</t>
+          <t>52,78; 273,4</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-54,24; 287,35</t>
+          <t>-48,59; 249,07</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-45,32; 309,08</t>
+          <t>-45,07; 315,69</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-10,02; 401,14</t>
+          <t>37,26; 510,36</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-23,33; 100,66</t>
+          <t>-20,01; 109,51</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-33,24; 77,79</t>
+          <t>-34,6; 67,8</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>38,33; 242,48</t>
+          <t>56,34; 249,01</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2,48</t>
+          <t>2,08</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>3,46</t>
+          <t>3,88</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>3,11</t>
+          <t>3,14</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>1,22; 5,4</t>
+          <t>1,06; 5,44</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-0,93; 2,4</t>
+          <t>-0,68; 2,44</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0,63; 4,47</t>
+          <t>0,42; 3,85</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-0,53; 2,79</t>
+          <t>-0,56; 2,81</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-2,01; 0,97</t>
+          <t>-2,09; 0,87</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,44; 5,02</t>
+          <t>2,17; 5,41</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0,67; 3,35</t>
+          <t>0,72; 3,39</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-0,96; 1,14</t>
+          <t>-0,93; 1,29</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1,69; 4,44</t>
+          <t>1,79; 4,31</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>189,76%</t>
+          <t>159,14%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>196,17%</t>
+          <t>220,07%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>196,02%</t>
+          <t>197,47%</t>
         </is>
       </c>
     </row>
@@ -1647,54 +1647,54 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>28,53; 1016,61</t>
+          <t>33,04; 921,53</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-49,2; 446,17</t>
+          <t>-40,33; 426,34</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-8,29; 813,27</t>
+          <t>-6,25; 656,78</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-23,19; 257,21</t>
+          <t>-28,37; 254,24</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-73,46; 123,2</t>
+          <t>-77,52; 101,65</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>38,51; 507,63</t>
+          <t>70,97; 618,76</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>26,41; 322,16</t>
+          <t>25,61; 318,61</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-45,48; 125,16</t>
+          <t>-42,15; 120,82</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>76,38; 494,22</t>
+          <t>71,0; 419,73</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1714,7 +1714,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>-1,67</t>
+          <t>-1,75</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>4,85</t>
+          <t>4,58</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>3,37</t>
+          <t>3,24</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-5,42; 0,55</t>
+          <t>-5,84; 0,49</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-6,16; -0,2</t>
+          <t>-5,94; -0,33</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-5,25; 3,81</t>
+          <t>-5,3; 3,57</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>2,01; 5,64</t>
+          <t>2,1; 5,44</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-0,11; 3,49</t>
+          <t>-0,17; 3,43</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>3,21; 6,9</t>
+          <t>2,72; 6,4</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>0,89; 4,04</t>
+          <t>0,98; 4,24</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-0,76; 2,26</t>
+          <t>-0,8; 2,17</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>1,82; 5,23</t>
+          <t>1,59; 5,04</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>-33,47%</t>
+          <t>-35,15%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>159,75%</t>
+          <t>150,88%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>98,94%</t>
+          <t>95,01%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-81,46; 25,19</t>
+          <t>-81,57; 26,13</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-88,18; 6,16</t>
+          <t>-89,53; 3,54</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-92,2; 107,79</t>
+          <t>-91,92; 121,89</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>51,46; 231,82</t>
+          <t>55,01; 229,68</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-1,53; 158,11</t>
+          <t>-4,92; 142,1</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>81,71; 290,03</t>
+          <t>67,83; 261,71</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>20,93; 150,25</t>
+          <t>25,3; 154,32</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-19,71; 75,49</t>
+          <t>-19,84; 79,89</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>43,21; 194,84</t>
+          <t>37,77; 174,25</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>0,24</t>
+          <t>0,51</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>2,19</t>
+          <t>2,63</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>1,24</t>
+          <t>1,59</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-1,16; 0,74</t>
+          <t>-1,15; 0,67</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-2,46; -0,76</t>
+          <t>-2,44; -0,75</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-0,92; 1,29</t>
+          <t>-0,41; 1,47</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>0,43; 2,37</t>
+          <t>0,5; 2,32</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-0,96; 0,87</t>
+          <t>-0,97; 0,95</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>1,1; 3,12</t>
+          <t>1,67; 3,42</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-0,03; 1,31</t>
+          <t>-0,07; 1,32</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-1,48; -0,21</t>
+          <t>-1,44; -0,24</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>0,38; 1,93</t>
+          <t>0,94; 2,23</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>12,64%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>69,44%</t>
+          <t>83,32%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>34,38%</t>
+          <t>44,3%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-25,52; 20,72</t>
+          <t>-25,51; 18,8</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-54,83; -20,44</t>
+          <t>-54,76; -20,73</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-20,1; 35,52</t>
+          <t>-9,67; 41,43</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>11,88; 90,85</t>
+          <t>12,81; 82,01</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-27,34; 31,04</t>
+          <t>-27,06; 34,26</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>32,67; 116,6</t>
+          <t>47,17; 126,06</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-0,61; 40,56</t>
+          <t>-1,63; 40,76</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-37,59; -6,04</t>
+          <t>-37,19; -6,57</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>9,6; 59,51</t>
+          <t>22,95; 68,12</t>
         </is>
       </c>
     </row>
